--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(SAR)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(SAR)cn.xlsx
@@ -480,7 +480,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -660,6 +660,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -669,7 +672,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -848,6 +851,9 @@
                   <c:v>10438324.181890992</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>10438324.181890992</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>10438324.181890992</c:v>
                 </c:pt>
               </c:numCache>
@@ -891,7 +897,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1071,6 +1077,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1080,7 +1089,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1260,6 +1269,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>18201846.466008939</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>18577567.752458461</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1302,7 +1314,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1482,6 +1494,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1491,7 +1506,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1671,6 +1686,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>7763522.2841179464</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>8139243.5705674682</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1692,11 +1710,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="438575104"/>
-        <c:axId val="438578560"/>
+        <c:axId val="459286400"/>
+        <c:axId val="459287936"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="438575104"/>
+        <c:axId val="459286400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1739,14 +1757,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="438578560"/>
+        <c:crossAx val="459287936"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="438578560"/>
+        <c:axId val="459287936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1797,7 +1815,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="438575104"/>
+        <c:crossAx val="459286400"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1988,7 +2006,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2168,6 +2186,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-658295.54002827872</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-1831256.2144501123</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2182,8 +2203,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="440935552"/>
-        <c:axId val="438615424"/>
+        <c:axId val="460525568"/>
+        <c:axId val="460521856"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2208,7 +2229,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2388,6 +2409,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2397,7 +2421,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2577,6 +2601,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2593,11 +2620,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="438611968"/>
-        <c:axId val="438613888"/>
+        <c:axId val="459299840"/>
+        <c:axId val="459305728"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="438611968"/>
+        <c:axId val="459299840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2640,14 +2667,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="438613888"/>
+        <c:crossAx val="459305728"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="438613888"/>
+        <c:axId val="459305728"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2698,12 +2725,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="438611968"/>
+        <c:crossAx val="459299840"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="438615424"/>
+        <c:axId val="460521856"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2740,12 +2767,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="440935552"/>
+        <c:crossAx val="460525568"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="440935552"/>
+        <c:axId val="460525568"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2754,7 +2781,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="438615424"/>
+        <c:crossAx val="460521856"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3163,7 +3190,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG62"/>
+  <dimension ref="A1:AG63"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -5967,6 +5994,47 @@
         <v>1</v>
       </c>
     </row>
+    <row r="63" spans="1:13" ht="12.75">
+      <c r="A63" s="11">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="12">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="12">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="13">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="13">
+        <v>-1831256.2144501123</v>
+      </c>
+      <c r="F63" s="14">
+        <v>-1435153.7473370298</v>
+      </c>
+      <c r="G63" s="14">
+        <v>10684880.666752618</v>
+      </c>
+      <c r="H63" s="14">
+        <v>13633907.975333851</v>
+      </c>
+      <c r="I63" s="14">
+        <v>10438324.181890992</v>
+      </c>
+      <c r="J63" s="14">
+        <v>18577567.752458461</v>
+      </c>
+      <c r="K63" s="14">
+        <v>8139243.5705674682</v>
+      </c>
+      <c r="L63" s="13">
+        <v>4943659.7771246117</v>
+      </c>
+      <c r="M63" s="8">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(SAR)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(SAR)cn.xlsx
@@ -480,7 +480,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -663,6 +663,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -672,7 +675,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -854,6 +857,9 @@
                   <c:v>10438324.181890992</c:v>
                 </c:pt>
                 <c:pt idx="60">
+                  <c:v>10438324.181890992</c:v>
+                </c:pt>
+                <c:pt idx="61">
                   <c:v>10438324.181890992</c:v>
                 </c:pt>
               </c:numCache>
@@ -897,7 +903,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1080,6 +1086,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1089,7 +1098,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1272,6 +1281,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>18577567.752458461</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>16771822.603890486</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1314,7 +1326,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1497,6 +1509,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1506,7 +1521,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1689,6 +1704,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>8139243.5705674682</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>6333498.4219994936</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1710,11 +1728,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="459286400"/>
-        <c:axId val="459287936"/>
+        <c:axId val="494352640"/>
+        <c:axId val="494354816"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="459286400"/>
+        <c:axId val="494352640"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1757,14 +1775,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="459287936"/>
+        <c:crossAx val="494354816"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="459287936"/>
+        <c:axId val="494354816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1815,7 +1833,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="459286400"/>
+        <c:crossAx val="494352640"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2006,7 +2024,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2189,6 +2207,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>-1831256.2144501123</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-629148.78444833402</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2203,8 +2224,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="460525568"/>
-        <c:axId val="460521856"/>
+        <c:axId val="494371584"/>
+        <c:axId val="494369024"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2229,7 +2250,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2412,6 +2433,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2421,7 +2445,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2604,6 +2628,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>1.2760000228881836</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1.1069999933242798</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2620,11 +2647,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="459299840"/>
-        <c:axId val="459305728"/>
+        <c:axId val="494365312"/>
+        <c:axId val="494367488"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="459299840"/>
+        <c:axId val="494365312"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2667,14 +2694,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="459305728"/>
+        <c:crossAx val="494367488"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="459305728"/>
+        <c:axId val="494367488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2725,12 +2752,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="459299840"/>
+        <c:crossAx val="494365312"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="460521856"/>
+        <c:axId val="494369024"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2767,12 +2794,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="460525568"/>
+        <c:crossAx val="494371584"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="460525568"/>
+        <c:axId val="494371584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2781,7 +2808,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="460521856"/>
+        <c:crossAx val="494369024"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3190,7 +3217,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG63"/>
+  <dimension ref="A1:AG64"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -6035,6 +6062,47 @@
         <v>1</v>
       </c>
     </row>
+    <row r="64" spans="1:13" ht="12.75">
+      <c r="A64" s="11">
+        <v>46234</v>
+      </c>
+      <c r="B64" s="12">
+        <v>1.1069999933242798</v>
+      </c>
+      <c r="C64" s="12">
+        <v>35.700000760000002</v>
+      </c>
+      <c r="D64" s="13">
+        <v>26.77592732691858</v>
+      </c>
+      <c r="E64" s="13">
+        <v>-629148.78444833402</v>
+      </c>
+      <c r="F64" s="14">
+        <v>-568336.7554131808</v>
+      </c>
+      <c r="G64" s="14">
+        <v>10116543.911339438</v>
+      </c>
+      <c r="H64" s="14">
+        <v>11199014.042317541</v>
+      </c>
+      <c r="I64" s="14">
+        <v>10438324.181890992</v>
+      </c>
+      <c r="J64" s="14">
+        <v>16771822.603890486</v>
+      </c>
+      <c r="K64" s="14">
+        <v>6333498.4219994936</v>
+      </c>
+      <c r="L64" s="13">
+        <v>5572808.5615729457</v>
+      </c>
+      <c r="M64" s="8">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(SAR)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(SAR)cn.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t>日期</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -75,10 +75,6 @@
   <si>
     <t>SAR</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>日期</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>每年投入本金</t>
@@ -480,7 +476,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -666,6 +662,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -675,7 +674,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -860,6 +859,9 @@
                   <c:v>10438324.181890992</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>10438324.181890992</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>10438324.181890992</c:v>
                 </c:pt>
               </c:numCache>
@@ -903,7 +905,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1089,6 +1091,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1098,7 +1103,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1284,6 +1289,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>16771822.603890486</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>16842638.102537446</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1326,7 +1334,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1512,6 +1520,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1521,7 +1532,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1707,6 +1718,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>6333498.4219994936</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>6404313.9206464533</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1728,11 +1742,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="494352640"/>
-        <c:axId val="494354816"/>
+        <c:axId val="367405696"/>
+        <c:axId val="367409408"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="494352640"/>
+        <c:axId val="367405696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1775,14 +1789,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="494354816"/>
+        <c:crossAx val="367409408"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="494354816"/>
+        <c:axId val="367409408"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1833,7 +1847,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="494352640"/>
+        <c:crossAx val="367405696"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2024,7 +2038,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2210,6 +2224,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-629148.78444833402</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-618346.8293536019</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2224,8 +2241,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="494371584"/>
-        <c:axId val="494369024"/>
+        <c:axId val="367649536"/>
+        <c:axId val="367642496"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2250,7 +2267,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2436,6 +2453,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2445,7 +2465,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2631,6 +2651,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2647,11 +2670,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="494365312"/>
-        <c:axId val="494367488"/>
+        <c:axId val="367598208"/>
+        <c:axId val="367640960"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="494365312"/>
+        <c:axId val="367598208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2694,14 +2717,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="494367488"/>
+        <c:crossAx val="367640960"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="494367488"/>
+        <c:axId val="367640960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2752,12 +2775,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="494365312"/>
+        <c:crossAx val="367598208"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="494369024"/>
+        <c:axId val="367642496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2794,12 +2817,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="494371584"/>
+        <c:crossAx val="367649536"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="494371584"/>
+        <c:axId val="367649536"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2808,7 +2831,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="494369024"/>
+        <c:crossAx val="367642496"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3217,7 +3240,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG64"/>
+  <dimension ref="A1:AG65"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -3351,28 +3374,28 @@
       </c>
       <c r="M3" s="8"/>
       <c r="P3" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="15" t="s">
+      <c r="R3" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="15" t="s">
+      <c r="S3" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="S3" s="15" t="s">
+      <c r="T3" s="15" t="s">
         <v>16</v>
-      </c>
-      <c r="T3" s="15" t="s">
-        <v>17</v>
       </c>
       <c r="U3" s="27" t="s">
         <v>11</v>
       </c>
       <c r="V3" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="W3" s="15" t="s">
         <v>18</v>
-      </c>
-      <c r="W3" s="15" t="s">
-        <v>19</v>
       </c>
       <c r="Y3" s="21">
         <v>44561</v>
@@ -6100,6 +6123,47 @@
         <v>5572808.5615729457</v>
       </c>
       <c r="M64" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="12.75">
+      <c r="A65" s="11">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="12">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="12">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="13">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="13">
+        <v>-618346.8293536019</v>
+      </c>
+      <c r="F65" s="14">
+        <v>-555068.98563595</v>
+      </c>
+      <c r="G65" s="14">
+        <v>9561474.9257034883</v>
+      </c>
+      <c r="H65" s="14">
+        <v>10651482.711610897</v>
+      </c>
+      <c r="I65" s="14">
+        <v>10438324.181890992</v>
+      </c>
+      <c r="J65" s="14">
+        <v>16842638.102537446</v>
+      </c>
+      <c r="K65" s="14">
+        <v>6404313.9206464533</v>
+      </c>
+      <c r="L65" s="13">
+        <v>6191155.3909265473</v>
+      </c>
+      <c r="M65" s="8">
         <v>1</v>
       </c>
     </row>
